--- a/no-basis/CurrentBuild/ValueSet-no-basis-documentreference-type.valueset.xlsx
+++ b/no-basis/CurrentBuild/ValueSet-no-basis-documentreference-type.valueset.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from unknown" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T20:52:01+00:00</t>
+    <t>2026-10-04T16:26:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
